--- a/pensum/ok06/OK06_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok06/OK06_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="159">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 6: Kapitalbehov og finansiering (V5)</t>
   </si>
@@ -164,18 +164,48 @@
     <t xml:space="preserve">a)  Kapitalbindingen i varelageret, i kroner. Regn først varekostnaden: salget uten mva ganger (1 − bruttofortjenesten). Gang så med lagringstiden og del på 360.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gjennomsnittlig varelager = budsjettert varekostnad × lagringstid / 360, eller varekostnad / omløpshastighet, der omløpshastighet = 360 / lagringstid (Økonomistyring 6.1.2). Bruttofortjeneste i prosent = bruttofortjeneste / salgsinntekt × 100 (kap. 5.1.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Kapitalbindingen i kundefordringene, i kroner: kredittsalget inkl. mva ganger kredittiden, delt på 360. Alt salget er kredittsalg.</t>
   </si>
   <si>
+    <t xml:space="preserve">Gjennomsnittlig utestående kundefordringer = kredittsalg inkl. mva × kredittid / 360 (Økonomistyring 6.1.3). Kundefordringer står i balansen inklusive mva.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Det samlede kapitalbehovet for avdelingen, i kroner: anleggsmidler + varelager + kundefordringer + likviditetsreserve.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kapital til investeringer + kapital til drift = totalt kapitalbehov (Økonomistyring 6.1, oppstillingen «Samlet kapitalbehov», og formelsamlingen kap. 6).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Tom regner varelageret av salget med mva: 6 000 000 × 0,65 × 45 / 360. Hvilken regel for mva er riktig?   A: Begge postene med mva, fordi alt Nordlys betaler for har mva   B: Varelageret uten mva, kundefordringene med mva   C: Begge postene uten mva, fordi mva er statens penger   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Grossisten gir rabatt hvis Nordlys kjøper paneler i store partier, men da ligger de i snitt 90 dager på lager i stedet for 45. Hva skjer med kapitalbehovet, og når lønner rabatten seg? To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Avsnitt 6.4: jo større partier og jo lenger varene ligger, jo større kapitalbehov. Kapitalkostnad = bundet kapital × rente. Egenkapital har også en kalkulatorisk kostnad (6.6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varekostnaden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trekk mva ut av salget først: 6 000 000 / 1,25 = 4 800 000. Bruttofortjeneste 35 % betyr at varekostnaden er 65 % av salget uten mva. Gang så med 45 / 360.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Med eller uten mva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varelageret uten mva: den inngående avgiften kommer tilbake. Kundefordringene med mva: kunden skylder hele fakturaen. Alt faktureres, så kredittsalget er hele salget med mva.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 6, avsnitt 6.1–6.1.4 og 6.4. Satsingen på solceller og ladepunkter: faktaarket for Nordlys; tallene for avdelingen er konstruert for oppgaven. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -233,12 +263,21 @@
     <t xml:space="preserve">a)  Kapitalbindingen i kundefordringene, i hele kroner: salget inkl. mva ganger kredittiden, delt på 360. Alt salget er kredittsalg.</t>
   </si>
   <si>
+    <t xml:space="preserve">Gjennomsnittlig utestående kundefordringer = kredittsalg inkl. mva × kredittid / 360 (Økonomistyring 6.1.3, formelsamlingen kap. 6).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Kapitalbindingen i varelageret, i kroner: materiellforbruket uten mva ganger lagringstiden, delt på 360.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kapitalbehov pga. lageroppbygging = materialforbruk første år × lagringstid / 360 (formelsamlingen kap. 6; Økonomistyring 6.1.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Det samlede kapitalbehovet ved oppstart, i hele kroner: utstyr + varelager + kundefordringer + likviditetsreserve.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kapital til investeringer + kapital til drift = totalt kapitalbehov (Økonomistyring 6.1, «Samlet kapitalbehov», og formelsamlingen kap. 6).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Hvilke poster hører hjemme i kapitalbehovet? Spør for hver post: må bedriften ha penger bundet her, eller er det leie, eller er det finansiering?</t>
   </si>
   <si>
@@ -263,6 +302,21 @@
     <t xml:space="preserve">e)  Kundene bruker 60 dager på å betale, ikke 30. Regn kundefordringene på nytt og skriv to setninger: hva skjer med kapitalbehovet, og hva bør eieren gjøre?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kundefordringer = kredittsalg inkl. mva × kredittid / 360 (6.1.3). Faktoring: ca. 80 % av fakturaen utbetales straks, kostnaden er 2–4 % av fakturabeløpet (6.9).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kundefordringene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salget med mva: 4 795 000 × 1,25. Gang med 30 / 360. Svaret er i underkant av en halv million.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva hører hjemme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hver post: må bedriften ha penger bundet her? Det som leies, binder ingen kapital. Lånet er der pengene kommer fra, ikke det de brukes til.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 6, avsnitt 6.1–6.1.4 og 6.9 (leasing). Salgsinntekter og materiell: resultatbudsjettet i kap. 9 (OK09 A2).</t>
   </si>
   <si>
@@ -326,18 +380,42 @@
     <t xml:space="preserve">a)  Egenkapitalen banken krever, i kroner: 30 % av hele kapitalbehovet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Egenkapital = egenkapitalandel × kapitalbehov. Samlet lånebehov = kapitalbehov − egenkapital (Økonomistyring 6.2.1 og 6.2.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Den langsiktige gjelda som minimum, i kroner: kravet til langsiktig kapital (anleggsmidler + halve varelageret) minus egenkapitalen.</t>
   </si>
   <si>
+    <t xml:space="preserve">Egenkapital + langsiktig gjeld = anleggsmidler + varelager / 2 (Økonomistyring 6.2.2). Kortsiktig lånebehov = samlet lånebehov − langsiktig lånebehov (6.2.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Annen kortsiktig gjeld, i kroner: den høyeste kortsiktige gjelda minus gjennomsnittlig leverandørgjeld (varekjøp inkl. mva × 15 / 360).</t>
   </si>
   <si>
+    <t xml:space="preserve">Gjennomsnittlig leverandørgjeld = kredittkjøp inkl. mva × kredittid / 360 (Økonomistyring 6.2.3; formelsamlingen kap. 6: «redusert kapitalbehov pga. leverandørkreditt»).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Tom sier: «Egenkapitalen er den billigste kilden. Den har jo ingen rente.» Hva sier boka?   A: Riktig: egenkapital har ingen rente og er den billigste kilden   B: Feil: eierne gir avkall på annen avkastning; kostnaden er kalkulatorisk og vises bare i det interne regnskapet   C: Feil: renten på egenkapitalen føres som finanskostnad i resultatregnskapet   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Kari og Tom skyter inn 300 000 kr i aksjekapital. Det er 16 % av kapitalbehovet, og banken krever 30 %. Hva kan de gjøre? Gi to tiltak og si hva hvert av dem koster eller betyr.</t>
   </si>
   <si>
+    <t xml:space="preserve">Egenkapitalandel = egenkapital / kapitalbehov. Kravet følger risikoen (6.2.1). Leasing (6.9), tilskudd fra offentlige organer (6.5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rekkefølgen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egenkapital først: 30 % av hele kapitalbehovet. Så kravet: anleggsmidler + halve varelageret. Langsiktig gjeld = kravet minus egenkapitalen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leverandørgjelda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varekjøp inkl. mva × 15 / 360. Kortsiktig gjeld høyst = kapitalbehov − egenkapital − langsiktig gjeld. Annen kortsiktig er resten.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 6, avsnitt 6.2–6.3 og 6.6. Tallene er øvingsheftets oppgave 2. Aksjekapitalen 300 000: faktaarket for Nordlys. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -386,16 +464,40 @@
     <t xml:space="preserve">a)  Egenkapitalandelen i prosent med én desimal: aksjekapitalen delt på kapitalbehovet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Egenkapitalandel = egenkapital × 100 / kapitalbehov. Kravet til egenkapital avhenger av risikoen (Økonomistyring 6.2.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Annen kortsiktig gjeld (kassekreditt og skyldige avgifter), i hele kroner: kapitalbehovet minus aksjekapital, banklån og gjennomsnittlig leverandørgjeld (varekjøp inkl. mva × 30 / 360).</t>
   </si>
   <si>
+    <t xml:space="preserve">Gjennomsnittlig leverandørgjeld = kredittkjøp inkl. mva × kredittid / 360. Annen kortsiktig gjeld = kapitalbehov − egenkapital − langsiktig gjeld − leverandørgjeld (Økonomistyring 6.2.3 og 6.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Den effektive renten på lånet, i prosent med to desimaler, når 7,5 % nominell rente avregnes månedlig: (1 + 0,075 / 12)^12 − 1.</t>
   </si>
   <si>
+    <t xml:space="preserve">rE = (1 + rN / m)^m − 1, der rN er nominell rente og m antall renteavregninger i året (Økonomistyring 6.7). Merk at formellinja i boka har feil eksponent; bokas egne utregninger bruker formen over (avviksregisteret).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Kundene bruker 60 dager på å betale i stedet for 30. Hva skjer med finansieringsplanen?   A: Ingenting: salget, lånet og aksjekapitalen er de samme   B: Kapitalbehovet stiger med 499 479 kr, og økningen må dekkes av kortsiktig gjeld eller mer egenkapital   C: Lånet dekker det, fordi 800 000 er mer enn kravet på 335 000   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Hva sier dere til banken? Skriv én setning om hvorfor planen er sunn ved 30 dager, og én om hva dere gjør hvis kundene bruker 60 dager.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krav til finansieringsplanen (6.2). Kassekreditt: provisjon på rammen pluss rente på det som brukes (6.8). Faktoring 2–4 % av fakturabeløpet (6.9). Effektiv rente (6.7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egenkapitalandelen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aksjekapital delt på kapitalbehov, ganger 100. Leverandørgjeld: 1 750 000 × 30 / 360. Trekk fra aksjekapital, lån og leverandørgjeld.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effektiv rente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,075 / 12 = 0,00625. Regn 1,00625 opphøyd i 12 på kalkulatoren, og trekk fra 1. Gang med 100 for prosent.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 6, avsnitt 6.2, 6.5, 6.7 og 6.8. Fjell Elektro AS: aksjekapital, lån og rente fra kap. 9 (OK09).</t>
@@ -409,7 +511,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -476,8 +578,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,6 +618,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFFBF6EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -546,7 +688,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -595,11 +737,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -632,8 +794,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -661,7 +823,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -964,7 +1126,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1151,35 +1313,20 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(500000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="B19" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(1700000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>48</v>
       </c>
@@ -1187,72 +1334,176 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(500000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(1700000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="11" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="27">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1266,13 +1517,20 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1289,7 +1547,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1300,7 +1558,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1310,7 +1568,7 @@
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1321,7 +1579,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1345,10 +1603,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1358,10 +1616,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1371,10 +1629,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1384,10 +1642,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1397,10 +1655,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1413,7 +1671,7 @@
         <v>36</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1436,10 +1694,10 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1477,7 +1735,7 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1489,187 +1747,276 @@
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(70000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(ABS(F21-(1019479))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
+      <c r="F22" s="10"/>
+      <c r="G22" s="11" t="str">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(70000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="11" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="10"/>
       <c r="G25" s="11" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F25="","",IF(ABS(F25-(1019479))&lt;=1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="11" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="11" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="11" t="str">
-        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-    </row>
-    <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="11" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="11" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="11" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="11" t="str">
+        <f aca="false">IF(F32="","",IF(UPPER(TRIM(F32))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="11" t="str">
+        <f aca="false">IF(F33="","",IF(UPPER(TRIM(F33))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="11" t="str">
+        <f aca="false">IF(F34="","",IF(UPPER(TRIM(F34))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="15"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+    </row>
+    <row r="46" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="34">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1684,19 +2031,26 @@
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B23:G23"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="B26:G26"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A30:G32"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A47:G47"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1713,7 +2067,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1724,7 +2078,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1734,7 +2088,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1745,7 +2099,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1769,10 +2123,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1782,10 +2136,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1795,10 +2149,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1808,10 +2162,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1821,10 +2175,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1834,10 +2188,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1847,10 +2201,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1860,10 +2214,10 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1888,7 +2242,7 @@
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1900,108 +2254,197 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(877500))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(228750))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(877500))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(228750))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="11" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="27">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2015,13 +2458,20 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2038,7 +2488,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2049,7 +2499,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2059,7 +2509,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2070,7 +2520,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2094,10 +2544,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2107,10 +2557,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2120,10 +2570,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2133,10 +2583,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2146,10 +2596,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2159,10 +2609,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2172,10 +2622,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2185,10 +2635,10 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2213,7 +2663,7 @@
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2225,108 +2675,197 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(73646))&lt;=2,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(7.76))&lt;=0.01,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(73646))&lt;=2,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
+    <row r="22" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(7.76))&lt;=0.01,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>150</v>
+      </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="11" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="27">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2340,13 +2879,20 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ok06/OK06_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok06/OK06_Klasseoppgaver_v5.xlsx
@@ -92,10 +92,10 @@
     <t xml:space="preserve">25 minutter · Helst alene. Sammen med sidemannen eller flere hvis du vil. Ark og blyant, appen (PC eller mobil) eller læreboka.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Kapitalbehovet er investeringene (anleggsmidlene) pluss det driften binder: varelager, kundefordringer og likviditetsreserve. Varelager = varekostnad × lagringstid / 360, uten mva. Kundefordringer = kredittsalg inkl. mva × kredittid / 360. Reserven er et beløp bedriften velger. Bruttofortjenesten regnes alltid av salget uten mva.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kari tror satsingen på solceller og ladepunkter blir stor, og vil gjøre den til en egen avdeling fra budsjettåret. Avdelingen trenger verktøy, måleutstyr og stillas for takarbeid for 240 000 kr og en varebil til 420 000 kr. Budsjettert salg første år er 6 000 000 kr inkludert mva, altså 4 800 000 kr uten. Bruttofortjenesten er 35 %, lavere enn i resten av Nordlys fordi panelene er en stor del av prisen. Alt faktureres med 30 dagers kredittid. Paneler og materiell ligger i snitt 45 dager på lager. Kari vil sette av en likviditetsreserve på 150 000 kr. Regn ut kapitalbehovet post for post. Gå fram slik: regn varekostnaden av salget uten mva; regn varelageret uten mva og kundefordringene med mva; bruk 360 dager i året; legg sammen.</t>
+    <t xml:space="preserve">Kort oppsummert: Kapitalbehovet er investeringene (anleggsmidlene) pluss det driften binder: varelager, kundefordringer og likviditetsreserve. Varelager = varekostnad × lagringstid / 360, uten merverdiavgift. Kundefordringer = kredittsalg med merverdiavgift × kredittid / 360. Reserven er et beløp bedriften velger. Bruttofortjenesten regnes alltid av salget uten merverdiavgift.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kari tror satsingen på solceller og ladepunkter blir stor, og vil gjøre den til en egen avdeling fra budsjettåret. Avdelingen trenger verktøy, måleutstyr og stillas for takarbeid for 240 000 kr og en varebil til 420 000 kr. Budsjettert salg første år er 6 000 000 kr med merverdiavgift (mva), altså 4 800 000 kr uten. Bruttofortjenesten er 35 %, lavere enn i resten av Nordlys fordi panelene er en stor del av prisen. Alt faktureres med 30 dagers kredittid. Paneler og materiell ligger i snitt 45 dager på lager. Kari vil sette av en likviditetsreserve på 150 000 kr. Regn ut kapitalbehovet post for post. Gå fram slik: regn varekostnaden av salget uten mva; regn varelageret uten mva og kundefordringene med mva; bruk 360 dager i året; legg sammen.</t>
   </si>
   <si>
     <t xml:space="preserve">Forutsetning</t>
@@ -116,16 +116,16 @@
     <t xml:space="preserve">420 000 kr</t>
   </si>
   <si>
-    <t xml:space="preserve">Salg første år</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 000 000 kr inkl. mva (4 800 000 uten)</t>
+    <t xml:space="preserve">Salg år 1, med merverdiavgift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 000 000 kr (4 800 000 kr uten)</t>
   </si>
   <si>
     <t xml:space="preserve">Bruttofortjeneste</t>
   </si>
   <si>
-    <t xml:space="preserve">35 % av salget uten mva</t>
+    <t xml:space="preserve">35 % av salget uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Kunder og kredittid</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">150 000 kr</t>
   </si>
   <si>
-    <t xml:space="preserve">Mva og dager i året</t>
+    <t xml:space="preserve">Merverdiavgift og dager i året</t>
   </si>
   <si>
     <t xml:space="preserve">25 % · 360 dager</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">Sjekk</t>
   </si>
   <si>
-    <t xml:space="preserve">a)  Kapitalbindingen i varelageret, i kroner. Regn først varekostnaden: salget uten mva ganger (1 − bruttofortjenesten). Gang så med lagringstiden og del på 360.</t>
+    <t xml:space="preserve">a)  Kapitalbindingen i varelageret, i kroner. Regn først varekostnaden: salget uten merverdiavgift ganger (1 − bruttofortjenesten). Gang så med lagringstiden og del på 360.</t>
   </si>
   <si>
     <t xml:space="preserve">Formel og begrep</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">Gjennomsnittlig varelager = budsjettert varekostnad × lagringstid / 360, eller varekostnad / omløpshastighet, der omløpshastighet = 360 / lagringstid (Økonomistyring 6.1.2). Bruttofortjeneste i prosent = bruttofortjeneste / salgsinntekt × 100 (kap. 5.1.2).</t>
   </si>
   <si>
-    <t xml:space="preserve">b)  Kapitalbindingen i kundefordringene, i kroner: kredittsalget inkl. mva ganger kredittiden, delt på 360. Alt salget er kredittsalg.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gjennomsnittlig utestående kundefordringer = kredittsalg inkl. mva × kredittid / 360 (Økonomistyring 6.1.3). Kundefordringer står i balansen inklusive mva.</t>
+    <t xml:space="preserve">b)  Kapitalbindingen i kundefordringene, i kroner: kredittsalget med merverdiavgift ganger kredittiden, delt på 360. Alt salget er kredittsalg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gjennomsnittlig utestående kundefordringer = kredittsalg med merverdiavgift × kredittid / 360 (Økonomistyring 6.1.3). Kundefordringer står i balansen inklusive merverdiavgift.</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Det samlede kapitalbehovet for avdelingen, i kroner: anleggsmidler + varelager + kundefordringer + likviditetsreserve.</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">Kapital til investeringer + kapital til drift = totalt kapitalbehov (Økonomistyring 6.1, oppstillingen «Samlet kapitalbehov», og formelsamlingen kap. 6).</t>
   </si>
   <si>
-    <t xml:space="preserve">d)  Tom regner varelageret av salget med mva: 6 000 000 × 0,65 × 45 / 360. Hvilken regel for mva er riktig?   A: Begge postene med mva, fordi alt Nordlys betaler for har mva   B: Varelageret uten mva, kundefordringene med mva   C: Begge postene uten mva, fordi mva er statens penger   (skriv bokstaven)</t>
+    <t xml:space="preserve">d)  Tom regner varelageret av salget med merverdiavgift: 6 000 000 × 0,65 × 45 / 360. Hvilken regel for merverdiavgift er riktig?   A: Begge postene med merverdiavgift, fordi alt Nordlys betaler for har merverdiavgift   B: Varelageret uten merverdiavgift, kundefordringene med merverdiavgift   C: Begge postene uten merverdiavgift, fordi merverdiavgift er statens penger   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Grossisten gir rabatt hvis Nordlys kjøper paneler i store partier, men da ligger de i snitt 90 dager på lager i stedet for 45. Hva skjer med kapitalbehovet, og når lønner rabatten seg? To–tre setninger.</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">Varekostnaden</t>
   </si>
   <si>
-    <t xml:space="preserve">Trekk mva ut av salget først: 6 000 000 / 1,25 = 4 800 000. Bruttofortjeneste 35 % betyr at varekostnaden er 65 % av salget uten mva. Gang så med 45 / 360.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Med eller uten mva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varelageret uten mva: den inngående avgiften kommer tilbake. Kundefordringene med mva: kunden skylder hele fakturaen. Alt faktureres, så kredittsalget er hele salget med mva.</t>
+    <t xml:space="preserve">Trekk merverdiavgift ut av salget først: 6 000 000 / 1,25 = 4 800 000. Bruttofortjeneste 35 % betyr at varekostnaden er 65 % av salget uten merverdiavgift. Gang så med 45 / 360.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Med eller uten merverdiavgift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varelageret uten merverdiavgift (mva): den inngående avgiften kommer tilbake. Kundefordringene med mva: kunden skylder hele fakturaen. Alt faktureres, så kredittsalget er hele salget med mva.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 6, avsnitt 6.1–6.1.4 og 6.4. Satsingen på solceller og ladepunkter: faktaarket for Nordlys; tallene for avdelingen er konstruert for oppgaven. Nordlys Elektro AS er en konstruert casebedrift.</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">Kort oppsummert: I en installasjonsbedrift er kundefordringene som regel den største posten i kapitalbehovet, fordi nesten alt salg faktureres. Kapitalbehovet er utstyr + varelager + kundefordringer + reserve. Det som leases, er ikke kapitalbehov; leia er en driftskostnad. Lånet er heller ikke kapitalbehov: lånet er en del av finansieringen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i kapittel 9) starter 1. januar. Resultatbudsjettet for første driftsår gir salgsinntekter på 4 795 000 kr uten mva og et materiellforbruk på 1 400 000 kr uten mva. Alle kundene får faktura med 30 dagers kredittid. Materiellet ligger i snitt 18 dager på lager. Utstyr og verktøy kjøpes for 300 000 kr. De to servicebilene leases. Eieren vil ha en likviditetsreserve på 150 000 kr, omtrent én måneds lønnsutbetaling. Finansieringen er aksjekapital 300 000 kr og banklån 500 000 kr. Regn ut kapitalbehovet post for post, med 25 % mva og 360 dager i året.</t>
+    <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i kapittel 9) starter 1. januar. Resultatbudsjettet for første driftsår gir salgsinntekter på 4 795 000 kr uten merverdiavgift (mva) og et materiellforbruk på 1 400 000 kr uten mva. Alle kundene får faktura med 30 dagers kredittid. Materiellet ligger i snitt 18 dager på lager. Utstyr og verktøy kjøpes for 300 000 kr. De to servicebilene leases. Eieren vil ha en likviditetsreserve på 150 000 kr, omtrent én måneds lønnsutbetaling. Finansieringen er aksjekapital 300 000 kr og banklån 500 000 kr. Regn ut kapitalbehovet post for post, med 25 % mva og 360 dager i året.</t>
   </si>
   <si>
     <t xml:space="preserve">Utstyr og verktøy</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">Salgsinntekter år 1</t>
   </si>
   <si>
-    <t xml:space="preserve">4 795 000 kr uten mva, alt på faktura</t>
+    <t xml:space="preserve">4 795 000 kr uten merverdiavgift, alt på faktura</t>
   </si>
   <si>
     <t xml:space="preserve">Kredittid til kundene</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">Materiellforbruk år 1</t>
   </si>
   <si>
-    <t xml:space="preserve">1 400 000 kr uten mva</t>
+    <t xml:space="preserve">1 400 000 kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">18 dager</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">Aksjekapital 300 000 + banklån 500 000</t>
   </si>
   <si>
-    <t xml:space="preserve">a)  Kapitalbindingen i kundefordringene, i hele kroner: salget inkl. mva ganger kredittiden, delt på 360. Alt salget er kredittsalg.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gjennomsnittlig utestående kundefordringer = kredittsalg inkl. mva × kredittid / 360 (Økonomistyring 6.1.3, formelsamlingen kap. 6).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b)  Kapitalbindingen i varelageret, i kroner: materiellforbruket uten mva ganger lagringstiden, delt på 360.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kapitalbehov pga. lageroppbygging = materialforbruk første år × lagringstid / 360 (formelsamlingen kap. 6; Økonomistyring 6.1.2).</t>
+    <t xml:space="preserve">a)  Kapitalbindingen i kundefordringene, i hele kroner: salget med merverdiavgift ganger kredittiden, delt på 360. Alt salget er kredittsalg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gjennomsnittlig utestående kundefordringer = kredittsalg med merverdiavgift × kredittid / 360 (Økonomistyring 6.1.3, formelsamlingen kap. 6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b)  Kapitalbindingen i varelageret, i kroner: materiellforbruket uten merverdiavgift ganger lagringstiden, delt på 360.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapitalbehov på grunn av lageroppbygging = materialforbruk første år × lagringstid / 360 (formelsamlingen kap. 6; Økonomistyring 6.1.2).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Det samlede kapitalbehovet ved oppstart, i hele kroner: utstyr + varelager + kundefordringer + likviditetsreserve.</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">e)  Kundene bruker 60 dager på å betale, ikke 30. Regn kundefordringene på nytt og skriv to setninger: hva skjer med kapitalbehovet, og hva bør eieren gjøre?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kundefordringer = kredittsalg inkl. mva × kredittid / 360 (6.1.3). Faktoring: ca. 80 % av fakturaen utbetales straks, kostnaden er 2–4 % av fakturabeløpet (6.9).</t>
+    <t xml:space="preserve">Kundefordringer = kredittsalg med merverdiavgift × kredittid / 360 (6.1.3). Faktoring: omtrent 80 % av fakturaen utbetales straks, kostnaden er 2–4 % av fakturabeløpet (6.9).</t>
   </si>
   <si>
     <t xml:space="preserve">Kundefordringene</t>
   </si>
   <si>
-    <t xml:space="preserve">Salget med mva: 4 795 000 × 1,25. Gang med 30 / 360. Svaret er i underkant av en halv million.</t>
+    <t xml:space="preserve">Salget med merverdiavgift: 4 795 000 × 1,25. Gang med 30 / 360. Svaret er i underkant av en halv million.</t>
   </si>
   <si>
     <t xml:space="preserve">Hva hører hjemme</t>
@@ -317,16 +317,16 @@
     <t xml:space="preserve">Spør for hver post: må bedriften ha penger bundet her? Det som leies, binder ingen kapital. Lånet er der pengene kommer fra, ikke det de brukes til.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 6, avsnitt 6.1–6.1.4 og 6.9 (leasing). Salgsinntekter og materiell: resultatbudsjettet i kap. 9 (OK09 A2).</t>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 6, avsnitt 6.1–6.1.4 og 6.9 (leasing). Salgsinntekter og materiell: resultatbudsjettet i kap. 9 (oppgave A2).</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys ved oppstart i 2019: finansieringsplanen</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: En fornuftig finansieringsplan har nok egenkapital, finansierer anleggsmidlene i sin helhet med langsiktig kapital, og lar den langsiktige kapitalen dekke en del av omløpsmidlene. Boka: egenkapital + langsiktig gjeld = anleggsmidler + halve varelageret. Det som er igjen av kapitalbehovet, er det høyeste den kortsiktige gjelda bør være. Leverandørgjeld = varekjøp inkl. mva × kredittid / 360.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kapitalbehovet for Nordlys ved oppstart i 2019 er 1 875 000 kr (del 1, slide 5): anleggsmidler 1 330 000, varelager 220 000, kundefordringer 125 000 og likviditetsreserve 200 000. Banken krever at egenkapitalen er minst 30 % av kapitalbehovet, og at egenkapital pluss langsiktig gjeld dekker anleggsmidlene og halve varelageret. Polarlys Elektro Grossist ga Nordlys som ny kunde bare 15 dagers kreditt det første året (senere ble det 30 dager), og varekjøpet første år er 4 950 000 kr inkl. mva. Sett opp finansieringsplanen trinn for trinn: egenkapital, samlet lånebehov, langsiktig gjeld (minimum), kortsiktig gjeld, leverandørgjeld og annen kortsiktig gjeld. Kontroller at summen blir kapitalbehovet.</t>
+    <t xml:space="preserve">Kort oppsummert: En fornuftig finansieringsplan har nok egenkapital, finansierer anleggsmidlene i sin helhet med langsiktig kapital, og lar den langsiktige kapitalen dekke en del av omløpsmidlene. Boka: egenkapital + langsiktig gjeld = anleggsmidler + halve varelageret. Det som er igjen av kapitalbehovet, er det høyeste den kortsiktige gjelda bør være. Leverandørgjeld = varekjøp med merverdiavgift × kredittid / 360.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapitalbehovet for Nordlys ved oppstart i 2019 er 1 875 000 kr (del 1, slide 5): anleggsmidler 1 330 000, varelager 220 000, kundefordringer 125 000 og likviditetsreserve 200 000. Banken krever at egenkapitalen er minst 30 % av kapitalbehovet, og at egenkapital pluss langsiktig gjeld dekker anleggsmidlene og halve varelageret. Polarlys Elektro Grossist ga Nordlys som ny kunde bare 15 dagers kreditt det første året (senere ble det 30 dager), og varekjøpet første år er 4 950 000 kr med merverdiavgift. Sett opp finansieringsplanen trinn for trinn: egenkapital, samlet lånebehov, langsiktig gjeld (minimum), kortsiktig gjeld, leverandørgjeld og annen kortsiktig gjeld. Kontroller at summen blir kapitalbehovet.</t>
   </si>
   <si>
     <t xml:space="preserve">Sum kapitalbehov (del 1)</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">Anleggsmidler + halve varelageret</t>
   </si>
   <si>
-    <t xml:space="preserve">Varekjøp inkl. mva</t>
+    <t xml:space="preserve">Varekjøp med merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">4 950 000 kr i året</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">Egenkapital + langsiktig gjeld = anleggsmidler + varelager / 2 (Økonomistyring 6.2.2). Kortsiktig lånebehov = samlet lånebehov − langsiktig lånebehov (6.2.3).</t>
   </si>
   <si>
-    <t xml:space="preserve">c)  Annen kortsiktig gjeld, i kroner: den høyeste kortsiktige gjelda minus gjennomsnittlig leverandørgjeld (varekjøp inkl. mva × 15 / 360).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gjennomsnittlig leverandørgjeld = kredittkjøp inkl. mva × kredittid / 360 (Økonomistyring 6.2.3; formelsamlingen kap. 6: «redusert kapitalbehov pga. leverandørkreditt»).</t>
+    <t xml:space="preserve">c)  Annen kortsiktig gjeld, i kroner: den høyeste kortsiktige gjelda minus gjennomsnittlig leverandørgjeld (varekjøp med merverdiavgift × 15 / 360).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gjennomsnittlig leverandørgjeld = kredittkjøp med merverdiavgift × kredittid / 360 (Økonomistyring 6.2.3; formelsamlingen kap. 6: «redusert kapitalbehov på grunn av leverandørkreditt»).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Tom sier: «Egenkapitalen er den billigste kilden. Den har jo ingen rente.» Hva sier boka?   A: Riktig: egenkapital har ingen rente og er den billigste kilden   B: Feil: eierne gir avkall på annen avkastning; kostnaden er kalkulatorisk og vises bare i det interne regnskapet   C: Feil: renten på egenkapitalen føres som finanskostnad i resultatregnskapet   (skriv bokstaven)</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">Leverandørgjelda</t>
   </si>
   <si>
-    <t xml:space="preserve">Varekjøp inkl. mva × 15 / 360. Kortsiktig gjeld høyst = kapitalbehov − egenkapital − langsiktig gjeld. Annen kortsiktig er resten.</t>
+    <t xml:space="preserve">Varekjøp med merverdiavgift × 15 / 360. Kortsiktig gjeld høyst = kapitalbehov − egenkapital − langsiktig gjeld. Annen kortsiktig er resten.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 6, avsnitt 6.2–6.3 og 6.6. Tallene er øvingsheftets oppgave 2. Aksjekapitalen 300 000: faktaarket for Nordlys. Nordlys Elektro AS er en konstruert casebedrift.</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">B2 · Din egen el-bedrift: finansieringsplanen og prisen på lånet</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Egenkapitalandelen er egenkapitalen delt på kapitalbehovet. Den faller når behovet stiger, selv om eierne har skutt inn like mye. Den langsiktige kapitalen skal dekke anleggsmidlene og halve varelageret; resten kan være kortsiktig gjeld som leverandørkreditt og kassekreditt. Effektiv rente = (1 + nominell rente / m)^m − 1, der m er antall renteavregninger i året. Lån sammenliknes på effektiv rente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kapitalbehovet for Fjell Elektro AS er 1 019 479 kr (oppgave A2): utstyr 300 000, varelager 70 000, kundefordringer 499 479 og reserve 150 000. Finansieringen er aksjekapital 300 000 kr og et serielån på 500 000 kr til 7,5 % nominell rente, med avdrag 100 000 kr i året. Renten avregnes månedlig. Grossisten gir 30 dagers kreditt, og varekjøpet er 1 750 000 kr inkl. mva. Banken krever minst 30 % egenkapital. Sjekk planen mot bokas krav, og regn ut hva lånet egentlig koster.</t>
+    <t xml:space="preserve">Kort oppsummert: Egenkapitalandelen er egenkapitalen delt på kapitalbehovet. Den faller når behovet stiger, selv om eierne har skutt inn like mye. Den langsiktige kapitalen skal dekke anleggsmidlene og halve varelageret; resten kan være kortsiktig gjeld som leverandørkreditt og kassekreditt. Effektiv rente = (1 + nominell rente / antall renteavregninger i året)^antall renteavregninger − 1. Lån sammenliknes på effektiv rente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapitalbehovet for Fjell Elektro AS er 1 019 479 kr (oppgave A2): utstyr 300 000, varelager 70 000, kundefordringer 499 479 og reserve 150 000. Finansieringen er aksjekapital 300 000 kr og et serielån på 500 000 kr til 7,5 % nominell rente, med avdrag 100 000 kr i året. Renten avregnes månedlig. Grossisten gir 30 dagers kreditt, og varekjøpet er 1 750 000 kr med merverdiavgift. Banken krever minst 30 % egenkapital. Sjekk planen mot bokas krav, og regn ut hva lånet egentlig koster.</t>
   </si>
   <si>
     <t xml:space="preserve">Kapitalbehov (A2)</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">Egenkapitalandel = egenkapital × 100 / kapitalbehov. Kravet til egenkapital avhenger av risikoen (Økonomistyring 6.2.1).</t>
   </si>
   <si>
-    <t xml:space="preserve">b)  Annen kortsiktig gjeld (kassekreditt og skyldige avgifter), i hele kroner: kapitalbehovet minus aksjekapital, banklån og gjennomsnittlig leverandørgjeld (varekjøp inkl. mva × 30 / 360).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gjennomsnittlig leverandørgjeld = kredittkjøp inkl. mva × kredittid / 360. Annen kortsiktig gjeld = kapitalbehov − egenkapital − langsiktig gjeld − leverandørgjeld (Økonomistyring 6.2.3 og 6.3).</t>
+    <t xml:space="preserve">b)  Annen kortsiktig gjeld (kassekreditt og skyldige avgifter), i hele kroner: kapitalbehovet minus aksjekapital, banklån og gjennomsnittlig leverandørgjeld (varekjøp med merverdiavgift × 30 / 360).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gjennomsnittlig leverandørgjeld = kredittkjøp med merverdiavgift × kredittid / 360. Annen kortsiktig gjeld = kapitalbehov − egenkapital − langsiktig gjeld − leverandørgjeld (Økonomistyring 6.2.3 og 6.3).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Den effektive renten på lånet, i prosent med to desimaler, når 7,5 % nominell rente avregnes månedlig: (1 + 0,075 / 12)^12 − 1.</t>
   </si>
   <si>
-    <t xml:space="preserve">rE = (1 + rN / m)^m − 1, der rN er nominell rente og m antall renteavregninger i året (Økonomistyring 6.7). Merk at formellinja i boka har feil eksponent; bokas egne utregninger bruker formen over (avviksregisteret).</t>
+    <t xml:space="preserve">Effektiv rente = (1 + nominell rente / antall renteavregninger i året)^antall renteavregninger − 1 (Økonomistyring 6.7). Merk at formellinja i boka har feil eksponent; bokas egne utregninger bruker formen over (avviksregisteret).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Kundene bruker 60 dager på å betale i stedet for 30. Hva skjer med finansieringsplanen?   A: Ingenting: salget, lånet og aksjekapitalen er de samme   B: Kapitalbehovet stiger med 499 479 kr, og økningen må dekkes av kortsiktig gjeld eller mer egenkapital   C: Lånet dekker det, fordi 800 000 er mer enn kravet på 335 000   (skriv bokstaven)</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">0,075 / 12 = 0,00625. Regn 1,00625 opphøyd i 12 på kalkulatoren, og trekk fra 1. Gang med 100 for prosent.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 6, avsnitt 6.2, 6.5, 6.7 og 6.8. Fjell Elektro AS: aksjekapital, lån og rente fra kap. 9 (OK09).</t>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 6, avsnitt 6.2, 6.5, 6.7 og 6.8. Fjell Elektro AS: aksjekapital, lån og rente fra kap. 9.</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1380,7 @@
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
         <v>52</v>
       </c>
@@ -1467,7 +1467,7 @@
       <c r="F36" s="18"/>
       <c r="G36" s="18"/>
     </row>
-    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
         <v>58</v>
       </c>
@@ -1967,7 +1967,7 @@
       <c r="F42" s="16"/>
       <c r="G42" s="16"/>
     </row>
-    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
         <v>93</v>
       </c>
@@ -2688,7 +2688,7 @@
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>147</v>
       </c>

--- a/pensum/ok06/OK06_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok06/OK06_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="159">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 6: Kapitalbehov og finansiering (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 6: Kapitalbehov og finansiering (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ok06/OK06_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok06/OK06_Klasseoppgaver_v5.xlsx
@@ -326,7 +326,7 @@
     <t xml:space="preserve">Kort oppsummert: En fornuftig finansieringsplan har nok egenkapital, finansierer anleggsmidlene i sin helhet med langsiktig kapital, og lar den langsiktige kapitalen dekke en del av omløpsmidlene. Boka: egenkapital + langsiktig gjeld = anleggsmidler + halve varelageret. Det som er igjen av kapitalbehovet, er det høyeste den kortsiktige gjelda bør være. Leverandørgjeld = varekjøp med merverdiavgift × kredittid / 360.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kapitalbehovet for Nordlys ved oppstart i 2019 er 1 875 000 kr (del 1, slide 5): anleggsmidler 1 330 000, varelager 220 000, kundefordringer 125 000 og likviditetsreserve 200 000. Banken krever at egenkapitalen er minst 30 % av kapitalbehovet, og at egenkapital pluss langsiktig gjeld dekker anleggsmidlene og halve varelageret. Polarlys Elektro Grossist ga Nordlys som ny kunde bare 15 dagers kreditt det første året (senere ble det 30 dager), og varekjøpet første år er 4 950 000 kr med merverdiavgift. Sett opp finansieringsplanen trinn for trinn: egenkapital, samlet lånebehov, langsiktig gjeld (minimum), kortsiktig gjeld, leverandørgjeld og annen kortsiktig gjeld. Kontroller at summen blir kapitalbehovet.</t>
+    <t xml:space="preserve">Kapitalbehovet for Nordlys ved oppstart i 2019 er 1 875 000 kr (del 1, slide 5): anleggsmidler 1 330 000, varelager 220 000, kundefordringer 125 000 og likviditetsreserve 200 000. Banken krever at egenkapitalen er minst 30 % av kapitalbehovet, og at egenkapital pluss langsiktig gjeld dekker anleggsmidlene og halve varelageret. Polarlys Elektro Grossist ga Nordlys som ny kunde bare 15 dagers kreditt det første året (senere ble det 30 dager), og varekjøpet første år er 4 950 000 kr med merverdiavgift (varekostnaden 3 960 000 × 1,25). Sett opp finansieringsplanen trinn for trinn: egenkapital, samlet lånebehov, langsiktig gjeld (minimum), kortsiktig gjeld, leverandørgjeld og annen kortsiktig gjeld. Kontroller at summen blir kapitalbehovet.</t>
   </si>
   <si>
     <t xml:space="preserve">Sum kapitalbehov (del 1)</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">Varekjøp med merverdiavgift</t>
   </si>
   <si>
-    <t xml:space="preserve">4 950 000 kr i året</t>
+    <t xml:space="preserve">3 960 000 × 1,25 = 4 950 000 kr</t>
   </si>
   <si>
     <t xml:space="preserve">Kreditt fra Polarlys</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">Kort oppsummert: Egenkapitalandelen er egenkapitalen delt på kapitalbehovet. Den faller når behovet stiger, selv om eierne har skutt inn like mye. Den langsiktige kapitalen skal dekke anleggsmidlene og halve varelageret; resten kan være kortsiktig gjeld som leverandørkreditt og kassekreditt. Effektiv rente = (1 + nominell rente / antall renteavregninger i året)^antall renteavregninger − 1. Lån sammenliknes på effektiv rente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kapitalbehovet for Fjell Elektro AS er 1 019 479 kr (oppgave A2): utstyr 300 000, varelager 70 000, kundefordringer 499 479 og reserve 150 000. Finansieringen er aksjekapital 300 000 kr og et serielån på 500 000 kr til 7,5 % nominell rente, med avdrag 100 000 kr i året. Renten avregnes månedlig. Grossisten gir 30 dagers kreditt, og varekjøpet er 1 750 000 kr med merverdiavgift. Banken krever minst 30 % egenkapital. Sjekk planen mot bokas krav, og regn ut hva lånet egentlig koster.</t>
+    <t xml:space="preserve">Kapitalbehovet for Fjell Elektro AS er 1 019 479 kr (oppgave A2): utstyr 300 000, varelager 70 000, kundefordringer 499 479 og reserve 150 000. Finansieringen er aksjekapital 300 000 kr og et serielån på 500 000 kr til 7,5 % nominell rente, med avdrag 100 000 kr i året. Renten avregnes månedlig. Grossisten gir 30 dagers kreditt, og varekjøpet er 1 750 000 kr med merverdiavgift (materiellet 1 400 000 × 1,25). Banken krever minst 30 % egenkapital. Sjekk planen mot bokas krav, og regn ut hva lånet egentlig koster.</t>
   </si>
   <si>
     <t xml:space="preserve">Kapitalbehov (A2)</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">7,5 % nominelt, avregnes månedlig</t>
   </si>
   <si>
-    <t xml:space="preserve">1 750 000 kr, 30 dagers kreditt</t>
+    <t xml:space="preserve">1 400 000 × 1,25 = 1 750 000 kr, 30 dager</t>
   </si>
   <si>
     <t xml:space="preserve">a)  Egenkapitalandelen i prosent med én desimal: aksjekapitalen delt på kapitalbehovet.</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">Egenkapitalandelen</t>
   </si>
   <si>
-    <t xml:space="preserve">Aksjekapital delt på kapitalbehov, ganger 100. Leverandørgjeld: 1 750 000 × 30 / 360. Trekk fra aksjekapital, lån og leverandørgjeld.</t>
+    <t xml:space="preserve">Aksjekapital delt på kapitalbehov, ganger 100. Leverandørgjeld: varekjøpet 1 400 000 × 1,25 = 1 750 000, × 30 / 360. Trekk fra aksjekapital, lån og leverandørgjeld.</t>
   </si>
   <si>
     <t xml:space="preserve">Effektiv rente</t>
